--- a/data/trans_dic/P55$pareja-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$pareja-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 77,06</t>
+          <t>9,68; 77,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,42</t>
+          <t>0,0; 49,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 63,35</t>
+          <t>8,89; 63,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,98; 63,3</t>
+          <t>30,57; 61,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,82</t>
+          <t>0,0; 45,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 36,07</t>
+          <t>6,83; 36,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 45,79</t>
+          <t>4,87; 44,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 28,02</t>
+          <t>8,99; 26,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 47,95</t>
+          <t>9,09; 50,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,62; 30,87</t>
+          <t>7,6; 32,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 42,24</t>
+          <t>8,01; 40,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,82; 40,26</t>
+          <t>21,47; 39,12</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 69,19</t>
+          <t>16,12; 66,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,11; 76,28</t>
+          <t>30,03; 77,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 54,33</t>
+          <t>8,12; 54,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,54; 56,42</t>
+          <t>11,64; 56,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,06</t>
+          <t>0,0; 28,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 25,92</t>
+          <t>4,89; 27,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 30,89</t>
+          <t>3,4; 28,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 21,9</t>
+          <t>7,25; 21,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,57; 37,86</t>
+          <t>10,5; 37,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,71; 41,72</t>
+          <t>17,02; 40,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 29,13</t>
+          <t>6,63; 28,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,85; 25,74</t>
+          <t>11,19; 25,56</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,2; 91,02</t>
+          <t>36,36; 90,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,87; 78,32</t>
+          <t>21,57; 75,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,35; 65,78</t>
+          <t>22,3; 66,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,78; 51,84</t>
+          <t>23,34; 50,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,45</t>
+          <t>0,0; 23,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,92; 70,36</t>
+          <t>17,65; 69,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 17,86</t>
+          <t>5,13; 17,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 27,11</t>
+          <t>6,16; 27,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 37,29</t>
+          <t>12,34; 42,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,41; 60,14</t>
+          <t>25,29; 61,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 27,11</t>
+          <t>13,22; 27,33</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,5; 93,96</t>
+          <t>47,52; 93,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,47; 56,04</t>
+          <t>15,48; 56,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,15; 82,92</t>
+          <t>36,56; 82,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 51,8</t>
+          <t>16,95; 51,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 33,87</t>
+          <t>8,09; 33,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 30,16</t>
+          <t>5,81; 29,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 33,1</t>
+          <t>4,24; 32,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 16,5</t>
+          <t>4,52; 17,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,11; 50,33</t>
+          <t>22,85; 50,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 33,48</t>
+          <t>11,97; 32,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 46,34</t>
+          <t>17,47; 45,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 25,01</t>
+          <t>10,26; 24,99</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,23; 89,34</t>
+          <t>24,35; 88,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,9</t>
+          <t>0,0; 83,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 42,08</t>
+          <t>5,57; 42,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,71</t>
+          <t>0,0; 37,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 44,14</t>
+          <t>8,53; 42,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 36,3</t>
+          <t>3,81; 34,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,23</t>
+          <t>0,0; 11,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,14; 50,85</t>
+          <t>13,91; 48,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 38,43</t>
+          <t>9,88; 40,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,61; 37,22</t>
+          <t>5,79; 37,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 18,67</t>
+          <t>1,89; 17,58</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,16; 63,92</t>
+          <t>22,75; 66,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,34; 71,14</t>
+          <t>29,42; 76,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,8; 65,44</t>
+          <t>16,58; 60,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 43,19</t>
+          <t>17,91; 42,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,57; 35,63</t>
+          <t>6,55; 36,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,95; 37,0</t>
+          <t>4,96; 36,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,58; 50,79</t>
+          <t>7,94; 47,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,54; 22,75</t>
+          <t>6,92; 22,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,08; 42,26</t>
+          <t>16,03; 41,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,06; 48,75</t>
+          <t>18,92; 48,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,65; 46,41</t>
+          <t>15,4; 48,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,5; 27,78</t>
+          <t>14,74; 27,89</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,86; 64,25</t>
+          <t>22,07; 64,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,63; 62,03</t>
+          <t>23,27; 63,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,49; 68,1</t>
+          <t>29,54; 67,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,47; 46,03</t>
+          <t>10,93; 44,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 19,86</t>
+          <t>2,15; 19,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,35; 31,03</t>
+          <t>6,96; 30,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,23; 36,93</t>
+          <t>12,88; 37,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,6; 22,93</t>
+          <t>9,23; 23,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,56; 30,63</t>
+          <t>9,55; 29,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,34; 36,65</t>
+          <t>16,69; 38,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,74; 42,91</t>
+          <t>20,87; 42,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,03; 26,25</t>
+          <t>11,48; 26,01</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,05; 57,66</t>
+          <t>25,6; 59,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,25; 52,32</t>
+          <t>9,28; 49,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,37; 69,94</t>
+          <t>29,18; 68,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,44; 73,63</t>
+          <t>35,09; 73,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,88; 26,33</t>
+          <t>5,09; 25,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,9; 30,09</t>
+          <t>6,85; 28,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 19,29</t>
+          <t>1,88; 19,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,2; 18,07</t>
+          <t>6,26; 18,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,34; 36,12</t>
+          <t>16,95; 35,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,78; 30,09</t>
+          <t>11,2; 32,15</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,23; 31,33</t>
+          <t>11,59; 31,6</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,49; 27,76</t>
+          <t>14,75; 28,49</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,63; 56,61</t>
+          <t>40,84; 57,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,16; 49,13</t>
+          <t>30,49; 47,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35,42; 52,5</t>
+          <t>35,67; 53,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29,59; 41,75</t>
+          <t>29,3; 42,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,62</t>
+          <t>7,21; 15,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,32; 19,87</t>
+          <t>11,36; 21,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,73; 22,81</t>
+          <t>12,59; 23,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,68; 14,7</t>
+          <t>9,68; 14,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,12; 28,97</t>
+          <t>19,7; 29,16</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,88; 28,37</t>
+          <t>19,21; 27,91</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21,5; 30,55</t>
+          <t>21,2; 30,33</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,16; 22,62</t>
+          <t>17,42; 22,56</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>831; 6680</t>
+          <t>839; 6693</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5821</t>
+          <t>0; 5819</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>797; 5701</t>
+          <t>800; 5757</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8105; 17112</t>
+          <t>8264; 16694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4488</t>
+          <t>0; 4674</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1987; 10256</t>
+          <t>1942; 10266</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1224; 11339</t>
+          <t>1207; 10936</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3233; 9216</t>
+          <t>2958; 8771</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1737; 9067</t>
+          <t>1719; 9490</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3063; 12415</t>
+          <t>3057; 12871</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2870; 14261</t>
+          <t>2704; 13774</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13078; 24128</t>
+          <t>12866; 23445</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2960; 11264</t>
+          <t>2624; 10830</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7317; 17940</t>
+          <t>7061; 18291</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1034; 6919</t>
+          <t>1034; 6998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2545; 8679</t>
+          <t>1791; 8730</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6599</t>
+          <t>0; 6507</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2057; 10971</t>
+          <t>2071; 11451</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1269; 11227</t>
+          <t>1237; 10359</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3972; 12044</t>
+          <t>3988; 11846</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4513; 14761</t>
+          <t>4092; 14669</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11001; 27477</t>
+          <t>11211; 26914</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3262; 14297</t>
+          <t>3254; 13979</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7635; 18119</t>
+          <t>7874; 17992</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3042; 9484</t>
+          <t>3788; 9476</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3293; 11277</t>
+          <t>3106; 10800</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3146; 9694</t>
+          <t>3286; 9756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6107; 13312</t>
+          <t>5994; 13003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1949</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6212</t>
+          <t>0; 6322</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3105; 12192</t>
+          <t>3058; 11957</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2249; 7956</t>
+          <t>2283; 7943</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2863; 12513</t>
+          <t>2843; 12670</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4248; 15246</t>
+          <t>5046; 17271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8469; 19282</t>
+          <t>8109; 19608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9362; 19038</t>
+          <t>9285; 19190</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6360; 12581</t>
+          <t>6363; 12572</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2980; 10794</t>
+          <t>2982; 10838</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5186; 11575</t>
+          <t>5103; 11479</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2997; 8571</t>
+          <t>2804; 8583</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2113; 10810</t>
+          <t>2583; 10700</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2906; 11903</t>
+          <t>2293; 11555</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1034; 9724</t>
+          <t>1245; 9600</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1609; 5925</t>
+          <t>1625; 6201</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10017; 22806</t>
+          <t>10352; 22791</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6840; 19662</t>
+          <t>7032; 19314</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7688; 20081</t>
+          <t>7572; 19860</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5651; 13121</t>
+          <t>5382; 13112</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2525; 7718</t>
+          <t>2104; 7681</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4138</t>
+          <t>0; 4143</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>440; 3364</t>
+          <t>445; 3407</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5109</t>
+          <t>0; 5802</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2158; 11149</t>
+          <t>2155; 10845</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>894; 8771</t>
+          <t>921; 8283</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1812</t>
+          <t>0; 1846</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3429; 12334</t>
+          <t>3374; 11694</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3249; 13158</t>
+          <t>3381; 13937</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1923; 10827</t>
+          <t>1684; 10884</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>523; 4505</t>
+          <t>457; 4242</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3802; 11486</t>
+          <t>4088; 11887</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5305; 12864</t>
+          <t>5320; 13809</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2509; 9774</t>
+          <t>2476; 9073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4467; 10447</t>
+          <t>4333; 10336</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1837; 9959</t>
+          <t>1830; 10229</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1053; 7874</t>
+          <t>1055; 7686</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1305; 11879</t>
+          <t>1857; 11154</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2380; 7182</t>
+          <t>2184; 7054</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7382; 19405</t>
+          <t>7360; 19049</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7501; 19191</t>
+          <t>7446; 19182</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5999; 17786</t>
+          <t>5901; 18631</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7530; 15491</t>
+          <t>8217; 15553</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4090; 12023</t>
+          <t>4130; 12097</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6636; 18192</t>
+          <t>6824; 18566</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7793; 17998</t>
+          <t>7808; 17881</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2899; 10699</t>
+          <t>2541; 10395</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>843; 7781</t>
+          <t>841; 7600</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3134; 15319</t>
+          <t>3438; 14953</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7450; 20802</t>
+          <t>7257; 20845</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4594; 12251</t>
+          <t>4931; 12795</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6110; 17732</t>
+          <t>5529; 17324</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12860; 28840</t>
+          <t>13137; 30629</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17988; 35511</t>
+          <t>17271; 34813</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9223; 20131</t>
+          <t>8807; 19942</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8140; 18739</t>
+          <t>8320; 19228</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1927; 10896</t>
+          <t>1933; 10211</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7761; 17300</t>
+          <t>7218; 16843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6025; 12518</t>
+          <t>5965; 12452</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2321; 12524</t>
+          <t>2419; 12216</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3235; 14109</t>
+          <t>3213; 13291</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1010; 10741</t>
+          <t>1046; 10839</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3645; 10615</t>
+          <t>3681; 10928</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13078; 28916</t>
+          <t>13573; 28521</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7301; 20378</t>
+          <t>7587; 21770</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9837; 25194</t>
+          <t>9323; 25407</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10976; 21029</t>
+          <t>11172; 21580</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>51428; 71659</t>
+          <t>51690; 72241</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>45551; 71809</t>
+          <t>44567; 69964</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43026; 63764</t>
+          <t>43323; 64488</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46470; 65574</t>
+          <t>46020; 66350</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>16804; 36065</t>
+          <t>16649; 34700</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31646; 55542</t>
+          <t>31763; 59367</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34048; 60975</t>
+          <t>33670; 62436</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>31775; 48243</t>
+          <t>31765; 47763</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>71914; 103582</t>
+          <t>70432; 104258</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>84626; 120774</t>
+          <t>81765; 118811</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>83602; 118789</t>
+          <t>82445; 117938</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>83271; 109756</t>
+          <t>84524; 109498</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$pareja-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$pareja-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 77,2</t>
+          <t>10,31; 77,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,41</t>
+          <t>0,0; 42,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 63,98</t>
+          <t>8,79; 64,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,57; 61,75</t>
+          <t>36,11; 65,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,63</t>
+          <t>0,0; 53,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 36,1</t>
+          <t>7,01; 35,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 44,16</t>
+          <t>4,73; 46,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,99; 26,66</t>
+          <t>9,31; 28,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 50,18</t>
+          <t>9,16; 51,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 32,01</t>
+          <t>7,52; 32,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 40,8</t>
+          <t>8,72; 40,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,47; 39,12</t>
+          <t>24,04; 42,52</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,12; 66,52</t>
+          <t>18,2; 69,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,03; 77,78</t>
+          <t>28,15; 78,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 54,96</t>
+          <t>0,0; 54,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,64; 56,75</t>
+          <t>16,34; 60,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,65</t>
+          <t>0,0; 32,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 27,05</t>
+          <t>2,69; 25,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 28,5</t>
+          <t>3,55; 30,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 21,54</t>
+          <t>7,08; 20,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 37,62</t>
+          <t>10,81; 39,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 40,87</t>
+          <t>16,85; 42,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 28,48</t>
+          <t>7,17; 28,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,19; 25,56</t>
+          <t>11,1; 26,54</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,36; 90,95</t>
+          <t>35,9; 91,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,57; 75,01</t>
+          <t>22,86; 78,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,3; 66,21</t>
+          <t>21,81; 66,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,34; 50,63</t>
+          <t>22,75; 50,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,86</t>
+          <t>0,0; 23,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,65; 69,0</t>
+          <t>17,24; 71,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 17,84</t>
+          <t>5,05; 17,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 27,44</t>
+          <t>6,31; 28,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 42,24</t>
+          <t>10,18; 38,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,29; 61,15</t>
+          <t>25,11; 60,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,22; 27,33</t>
+          <t>12,84; 26,46</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,52; 93,89</t>
+          <t>50,76; 93,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 56,26</t>
+          <t>15,57; 55,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,56; 82,24</t>
+          <t>36,75; 82,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,95; 51,87</t>
+          <t>16,38; 51,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 33,52</t>
+          <t>6,41; 33,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 29,28</t>
+          <t>5,32; 29,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 32,67</t>
+          <t>3,43; 35,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 17,26</t>
+          <t>4,63; 17,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,85; 50,3</t>
+          <t>21,39; 49,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,97; 32,89</t>
+          <t>12,1; 34,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,47; 45,82</t>
+          <t>17,87; 45,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 24,99</t>
+          <t>10,52; 25,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,35; 88,91</t>
+          <t>30,46; 90,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,17</t>
+          <t>0,0; 74,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,99</t>
+          <t>0,0; 83,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 42,62</t>
+          <t>5,74; 44,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,15</t>
+          <t>0,0; 36,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 42,93</t>
+          <t>8,51; 44,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 34,28</t>
+          <t>0,0; 35,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,44</t>
+          <t>0,0; 11,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,91; 48,21</t>
+          <t>13,41; 48,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,88; 40,71</t>
+          <t>9,8; 41,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 37,41</t>
+          <t>6,18; 38,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 17,58</t>
+          <t>2,05; 18,49</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,75; 66,15</t>
+          <t>21,15; 63,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,42; 76,37</t>
+          <t>29,37; 76,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,58; 60,75</t>
+          <t>16,52; 62,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,91; 42,73</t>
+          <t>18,11; 41,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,55; 36,59</t>
+          <t>6,55; 40,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,96; 36,11</t>
+          <t>4,94; 35,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,94; 47,69</t>
+          <t>4,97; 46,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,92; 22,35</t>
+          <t>6,86; 21,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,03; 41,48</t>
+          <t>15,39; 40,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,92; 48,73</t>
+          <t>19,11; 48,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,4; 48,61</t>
+          <t>15,95; 47,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,74; 27,89</t>
+          <t>13,86; 27,88</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,07; 64,65</t>
+          <t>19,48; 64,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,27; 63,31</t>
+          <t>23,17; 61,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,54; 67,66</t>
+          <t>30,2; 68,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,93; 44,72</t>
+          <t>11,63; 43,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 19,4</t>
+          <t>2,21; 20,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 30,29</t>
+          <t>7,89; 30,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,88; 37,01</t>
+          <t>13,13; 36,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,23; 23,94</t>
+          <t>10,02; 24,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 29,93</t>
+          <t>10,59; 29,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,69; 38,92</t>
+          <t>15,84; 36,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,87; 42,07</t>
+          <t>22,21; 42,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,48; 26,01</t>
+          <t>11,91; 26,13</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,6; 59,16</t>
+          <t>26,01; 57,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,28; 49,03</t>
+          <t>9,96; 52,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,18; 68,09</t>
+          <t>29,66; 68,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,09; 73,24</t>
+          <t>35,82; 75,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,09; 25,69</t>
+          <t>5,16; 27,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,85; 28,34</t>
+          <t>6,82; 28,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 19,47</t>
+          <t>1,86; 20,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 18,6</t>
+          <t>5,4; 16,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,95; 35,63</t>
+          <t>15,62; 34,96</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,2; 32,15</t>
+          <t>9,82; 31,33</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11,59; 31,6</t>
+          <t>11,72; 30,45</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,75; 28,49</t>
+          <t>14,7; 28,33</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,84; 57,07</t>
+          <t>39,28; 58,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30,49; 47,87</t>
+          <t>30,9; 49,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35,67; 53,09</t>
+          <t>36,68; 53,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29,3; 42,24</t>
+          <t>31,0; 42,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,03</t>
+          <t>7,31; 15,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,36; 21,24</t>
+          <t>11,36; 20,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,59; 23,35</t>
+          <t>12,79; 22,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,68; 14,55</t>
+          <t>10,18; 15,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,7; 29,16</t>
+          <t>19,94; 28,91</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,21; 27,91</t>
+          <t>19,4; 28,1</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21,2; 30,33</t>
+          <t>20,94; 30,71</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,42; 22,56</t>
+          <t>17,56; 23,16</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>20665</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>839; 6693</t>
+          <t>894; 6750</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5819</t>
+          <t>0; 5016</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>800; 5757</t>
+          <t>791; 5764</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8264; 16694</t>
+          <t>10556; 19152</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4674</t>
+          <t>0; 5507</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1942; 10266</t>
+          <t>1995; 10134</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1207; 10936</t>
+          <t>1172; 11437</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2958; 8771</t>
+          <t>3127; 9532</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1719; 9490</t>
+          <t>1733; 9691</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3057; 12871</t>
+          <t>3023; 12967</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2704; 13774</t>
+          <t>2943; 13620</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12866; 23445</t>
+          <t>15103; 26715</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>13303</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2624; 10830</t>
+          <t>2963; 11314</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7061; 18291</t>
+          <t>6619; 18530</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1034; 6998</t>
+          <t>0; 6972</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1791; 8730</t>
+          <t>2691; 9896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6507</t>
+          <t>0; 7323</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2071; 11451</t>
+          <t>1139; 10807</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1237; 10359</t>
+          <t>1290; 11232</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3988; 11846</t>
+          <t>4144; 12238</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4092; 14669</t>
+          <t>4213; 15444</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11211; 26914</t>
+          <t>11096; 27751</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3254; 13979</t>
+          <t>3520; 14119</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7874; 17992</t>
+          <t>8323; 19906</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>13554</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3788; 9476</t>
+          <t>3741; 9482</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3106; 10800</t>
+          <t>3291; 11328</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3286; 9756</t>
+          <t>3214; 9803</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5994; 13003</t>
+          <t>5737; 12767</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6322</t>
+          <t>0; 6263</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3058; 11957</t>
+          <t>2988; 12319</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2283; 7943</t>
+          <t>2254; 7742</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2843; 12670</t>
+          <t>2914; 13090</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5046; 17271</t>
+          <t>4161; 15628</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8109; 19608</t>
+          <t>8052; 19274</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9285; 19190</t>
+          <t>8968; 18478</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>9474</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6363; 12572</t>
+          <t>6797; 12564</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2982; 10838</t>
+          <t>3000; 10779</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5103; 11479</t>
+          <t>5129; 11514</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2804; 8583</t>
+          <t>2909; 9161</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2583; 10700</t>
+          <t>2045; 10584</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2293; 11555</t>
+          <t>2100; 11782</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1245; 9600</t>
+          <t>1007; 10355</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1625; 6201</t>
+          <t>1760; 6657</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10352; 22791</t>
+          <t>9690; 22525</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7032; 19314</t>
+          <t>7107; 20153</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7572; 19860</t>
+          <t>7745; 19531</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5382; 13112</t>
+          <t>5866; 13995</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>397</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1919</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2104; 7681</t>
+          <t>2631; 7779</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5580</t>
+          <t>0; 6652</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4143</t>
+          <t>0; 4128</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>445; 3407</t>
+          <t>470; 3640</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5802</t>
+          <t>0; 5747</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2155; 10845</t>
+          <t>2150; 11145</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>921; 8283</t>
+          <t>0; 8485</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1846</t>
+          <t>0; 2014</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3374; 11694</t>
+          <t>3253; 11768</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3381; 13937</t>
+          <t>3356; 14048</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1684; 10884</t>
+          <t>1797; 11242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>457; 4242</t>
+          <t>513; 4622</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11389</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4088; 11887</t>
+          <t>3801; 11413</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5320; 13809</t>
+          <t>5310; 13814</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2476; 9073</t>
+          <t>2467; 9278</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4333; 10336</t>
+          <t>4386; 10130</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1830; 10229</t>
+          <t>1830; 11247</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1055; 7686</t>
+          <t>1051; 7578</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1857; 11154</t>
+          <t>1162; 10929</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2184; 7054</t>
+          <t>2205; 6881</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7360; 19049</t>
+          <t>7066; 18517</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7446; 19182</t>
+          <t>7524; 19264</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5901; 18631</t>
+          <t>6111; 18105</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8217; 15553</t>
+          <t>7814; 15719</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13856</t>
+          <t>17479</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4130; 12097</t>
+          <t>3646; 12081</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6824; 18566</t>
+          <t>6795; 17960</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7808; 17881</t>
+          <t>7982; 18037</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2541; 10395</t>
+          <t>3327; 12332</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>841; 7600</t>
+          <t>866; 8075</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3438; 14953</t>
+          <t>3893; 15276</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7257; 20845</t>
+          <t>7393; 20640</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4931; 12795</t>
+          <t>6540; 15785</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5529; 17324</t>
+          <t>6128; 16902</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13137; 30629</t>
+          <t>12461; 29024</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17271; 34813</t>
+          <t>18380; 35446</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8807; 19942</t>
+          <t>11178; 24529</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>18157</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8320; 19228</t>
+          <t>8454; 18695</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1933; 10211</t>
+          <t>2075; 10961</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7218; 16843</t>
+          <t>7336; 16934</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5965; 12452</t>
+          <t>6957; 14599</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2419; 12216</t>
+          <t>2453; 13095</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3213; 13291</t>
+          <t>3199; 13562</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1046; 10839</t>
+          <t>1035; 11147</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3681; 10928</t>
+          <t>3688; 11524</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13573; 28521</t>
+          <t>12506; 27985</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7587; 21770</t>
+          <t>6649; 21216</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9323; 25407</t>
+          <t>9426; 24483</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11172; 21580</t>
+          <t>12894; 24851</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>61755</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95666</t>
+          <t>105940</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>51690; 72241</t>
+          <t>49719; 73993</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>44567; 69964</t>
+          <t>45161; 71663</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43323; 64488</t>
+          <t>44557; 64999</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46020; 66350</t>
+          <t>52421; 72556</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>16649; 34700</t>
+          <t>16892; 35436</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31763; 59367</t>
+          <t>31767; 56176</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33670; 62436</t>
+          <t>34196; 60696</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>31765; 47763</t>
+          <t>36380; 54257</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>70432; 104258</t>
+          <t>71300; 103352</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>81765; 118811</t>
+          <t>82601; 119601</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>82445; 117938</t>
+          <t>81430; 119400</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>84524; 109498</t>
+          <t>92447; 121905</t>
         </is>
       </c>
     </row>
